--- a/files/programming-tasks/programmieraufgaben_bechtel.xlsx
+++ b/files/programming-tasks/programmieraufgaben_bechtel.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\hefl\files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\hefl\files\programming-tasks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40233482-9CFA-4275-B2AF-6BF36F121FBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E500396-3F47-4256-919F-7CEE73B11F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="25860" windowHeight="20805" tabRatio="540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aufgaben" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="89">
   <si>
     <t>id</t>
   </si>
@@ -760,12 +760,57 @@
     unittest.main()
 </t>
   </si>
+  <si>
+    <t>testClassName</t>
+  </si>
+  <si>
+    <t>runMethod</t>
+  </si>
+  <si>
+    <t>input</t>
+  </si>
+  <si>
+    <t>gruesse</t>
+  </si>
+  <si>
+    <t>"Anna"</t>
+  </si>
+  <si>
+    <t>pizza_bestellung</t>
+  </si>
+  <si>
+    <t>"Salami"</t>
+  </si>
+  <si>
+    <t>benutzer@example.com</t>
+  </si>
+  <si>
+    <t>ist_email</t>
+  </si>
+  <si>
+    <t>muenzwurf_simulieren</t>
+  </si>
+  <si>
+    <t>berechne_gesamtpreis</t>
+  </si>
+  <si>
+    <t>ist_schaltjahr</t>
+  </si>
+  <si>
+    <t>["Banane", "Butter", "Yoghurt", "Käse", "Milch", "Nutella", "Schokolade", "Chips", "Schinken"], 3</t>
+  </si>
+  <si>
+    <t>gesamtfläche_schachbrett</t>
+  </si>
+  <si>
+    <t>test_main.py</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -807,6 +852,14 @@
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -832,10 +885,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -889,8 +943,15 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1194,7 +1255,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
@@ -1205,12 +1266,15 @@
     <col min="8" max="8" width="72.7109375" style="7" customWidth="1"/>
     <col min="9" max="9" width="23.7109375" style="9" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="69.28515625" customWidth="1"/>
-    <col min="12" max="12" width="24.140625" customWidth="1"/>
-    <col min="13" max="16" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.28515625" customWidth="1"/>
+    <col min="12" max="12" width="27.140625" customWidth="1"/>
+    <col min="13" max="13" width="41.5703125" customWidth="1"/>
+    <col min="14" max="14" width="69.28515625" customWidth="1"/>
+    <col min="15" max="15" width="24.140625" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>4</v>
       </c>
@@ -1241,14 +1305,23 @@
       <c r="J1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="M1" t="s">
+        <v>76</v>
+      </c>
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="L1" t="s">
+      <c r="O1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="2" customFormat="1" ht="285" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" s="2" customFormat="1" ht="285" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
         <v>1</v>
       </c>
@@ -1279,14 +1352,23 @@
       <c r="J2" s="3">
         <v>0</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N2" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="O2" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="2" customFormat="1" ht="285" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" s="2" customFormat="1" ht="285" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <v>2</v>
       </c>
@@ -1317,14 +1399,23 @@
       <c r="J3" s="3">
         <v>0</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="N3" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="O3" s="7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="9" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" s="9" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" s="10">
         <v>3</v>
       </c>
@@ -1355,14 +1446,23 @@
       <c r="J4" s="1">
         <v>0</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="M4" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="N4" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="O4" s="7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="255" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="255" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
         <v>4</v>
       </c>
@@ -1393,11 +1493,17 @@
       <c r="J5" s="1">
         <v>0</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="K5" t="s">
+        <v>88</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="N5" s="7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="300" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="300" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
         <v>5</v>
       </c>
@@ -1428,14 +1534,23 @@
       <c r="J6" s="1">
         <v>0</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="K6" t="s">
+        <v>88</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="M6">
+        <v>2024</v>
+      </c>
+      <c r="N6" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="O6" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="393" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="393" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10">
         <v>9</v>
       </c>
@@ -1466,11 +1581,20 @@
       <c r="J7" s="1">
         <v>0</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K7" t="s">
+        <v>88</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="M7" t="s">
+        <v>86</v>
+      </c>
+      <c r="N7" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="270" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="270" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>10</v>
       </c>
@@ -1501,13 +1625,22 @@
       <c r="J8" s="1">
         <v>0</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="K8" t="s">
+        <v>88</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="N8" s="2" t="s">
         <v>57</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="M4" r:id="rId1" xr:uid="{5173C394-27F0-4C77-B4F2-7E8CD11E831F}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/files/programming-tasks/programmieraufgaben_bechtel.xlsx
+++ b/files/programming-tasks/programmieraufgaben_bechtel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\hefl\files\programming-tasks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C541143D-68E4-4DCB-A112-816C6FDED0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB872DDF-2BF3-444C-B676-7EDADE10F757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25650" yWindow="240" windowWidth="39615" windowHeight="20505" tabRatio="540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15" yWindow="90" windowWidth="25860" windowHeight="20805" tabRatio="540" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aufgaben" sheetId="1" r:id="rId1"/>
@@ -389,14 +389,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">def berechne_flaeche(seitenlänge):
-#deine Lösung
-def gesamtflaeche_schachbrett():
-#deine Lösung
-print gesamtflaeche_schachbrett()
-</t>
-  </si>
-  <si>
     <t>Wenn wir einer Liste ans Ende neue Elemente hinzufügen möchte, kann man die append()-Funktion verwenden. Man benutzt sie so:
 liste = ["Baum", "Wiese", "Garten"] 
 liste.append("Blumen")
@@ -424,6 +416,14 @@
         self.assertEqual(gesamtflaeche_schachbrett(), 256)
 if __name__ == '__main__':
     unittest.main()
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">def berechne_flaeche(seitenlänge):
+#deine Lösung
+def gesamtflaeche_schachbrett():
+#deine Lösung
+print (gesamtflaeche_schachbrett())
 </t>
   </si>
 </sst>
@@ -1038,7 +1038,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:16" s="23" customFormat="1" ht="315" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" s="23" customFormat="1" ht="360" x14ac:dyDescent="0.25">
       <c r="A3" s="16">
         <v>2</v>
       </c>
@@ -1155,13 +1155,13 @@
         <v>39</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G5" s="23" t="s">
         <v>45</v>
       </c>
       <c r="H5" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I5" s="17" t="s">
         <v>19</v>
@@ -1205,7 +1205,7 @@
         <v>69</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H6" s="32" t="s">
         <v>70</v>
@@ -1361,7 +1361,7 @@
         <v>37</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">

--- a/files/programming-tasks/programmieraufgaben_bechtel.xlsx
+++ b/files/programming-tasks/programmieraufgaben_bechtel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\hefl\files\programming-tasks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB872DDF-2BF3-444C-B676-7EDADE10F757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52149547-5583-449C-AA03-DA4490F1BB05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="90" windowWidth="25860" windowHeight="20805" tabRatio="540" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18465" yWindow="0" windowWidth="25890" windowHeight="20805" tabRatio="540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aufgaben" sheetId="1" r:id="rId1"/>
@@ -1038,7 +1038,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:16" s="23" customFormat="1" ht="360" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" s="23" customFormat="1" ht="315" x14ac:dyDescent="0.25">
       <c r="A3" s="16">
         <v>2</v>
       </c>

--- a/files/programming-tasks/programmieraufgaben_bechtel.xlsx
+++ b/files/programming-tasks/programmieraufgaben_bechtel.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\hefl\files\programming-tasks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52149547-5583-449C-AA03-DA4490F1BB05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFDC9AEF-5842-41E0-A02B-4A75856D8CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18465" yWindow="0" windowWidth="25890" windowHeight="20805" tabRatio="540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aufgaben" sheetId="1" r:id="rId1"/>
     <sheet name="Codegerueste" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" calcOnSave="0" concurrentCalc="0"/>
 </workbook>
 </file>
 
@@ -320,12 +320,6 @@
     <t>Die Funktion ist_gerade überprüft, ob eine übergebene Zahl gerade oder ungerade ist. Sie verwendet den Modulo-Operator (%), um zu prüfen, ob die Division der Zahl durch 2 einen Rest ergibt. Falls der Rest gleich Null ist, handelt es sich um eine gerade Zahl, andernfalls um eine ungerade Zahl.</t>
   </si>
   <si>
-    <t>Schreibe eine Funkton pizza_bestellung(pizza), die den Benutzer nach seiner Lieblingspizza fragt und eine entsprechende Nachrichtmit 'return' zurückgibt.
-Allerdings soll hier erstmal zwischen Margherita und Hawaii unterschieden werden.
-Bei Margherita soll: "Eine klassische Wahl! Gute Entscheidung.",
-bei Hawaii soll: "Ananas auf Pizza? Du bist mutig!" ausgegeben werden.</t>
-  </si>
-  <si>
     <t>import unittest
 from pizza import pizza_bestellung
 class TestPizzaBestellung(unittest.TestCase):
@@ -337,15 +331,6 @@
         self.assertEqual(result, "Ananas auf Pizza? Du bist mutig!")
 if __name__ == '__main__':
     unittest.main()</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Schreibe eine Funkton pizza_bestellung(pizza), die den Benutzer nach seiner Lieblingspizza fragt und eine entsprechende Nachrichtmit 'return' zurückgibt.&lt;/p&gt;
-&lt;br&gt;
-&lt;p&gt;Allerdings soll hier erstmal zwischen Margherita und Hawaii unterschieden werden.&lt;/p&gt;
-&lt;br&gt;
-&lt;p&gt;Bei Magherita soll: "Eine klassische Wahl! Gute Entscheidung.",
-bei Hawaii soll: "Ananas auf Pizza? Du bist mutig!" zurückgegeben werden.&lt;/p&gt;
-</t>
   </si>
   <si>
     <t>Die Funktion enthaelt_python prüft, ob der übergebene Text das Wort "Python" enthält. Dabei wird der in-Operator verwendet, um zu überprüfen, ob die Zeichenkette "Python" im Text vorhanden ist.</t>
@@ -425,6 +410,20 @@
 #deine Lösung
 print (gesamtflaeche_schachbrett())
 </t>
+  </si>
+  <si>
+    <t>&lt;p&gt;Schreibe eine Funktion pizza_bestellung(pizza), die den Namen der Lieblingspizza eines Benutzers entgegennimmt und eine entsprechende Nachricht mit 'return' zurückgibt..&lt;/p&gt;
+&lt;br&gt;
+&lt;p&gt;Allerdings soll hier erstmal zwischen Margherita und Hawaii unterschieden werden.&lt;/p&gt;
+&lt;br&gt;
+&lt;p&gt;Bei Margherita soll: "Eine klassische Wahl! Gute Entscheidung.",
+bei Hawaii soll: "Ananas auf Pizza? Du bist mutig!" zurückgegeben werden.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>Schreibe eine Funktion pizza_bestellung(pizza), die den Namen der Lieblingspizza eines Benutzers entgegennimmt und eine entsprechende Nachricht mit 'return' zurückgibt.
+Allerdings soll hier erstmal zwischen Margherita und Hawaii unterschieden werden.
+Bei Margherita soll: "Eine klassische Wahl! Gute Entscheidung.",
+bei Hawaii soll: "Ananas auf Pizza? Du bist mutig!" ausgegeben werden.</t>
   </si>
 </sst>
 </file>
@@ -1055,13 +1054,13 @@
         <v>23</v>
       </c>
       <c r="F3" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="G3" s="20" t="s">
-        <v>64</v>
-      </c>
       <c r="H3" s="18" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="I3" s="21" t="s">
         <v>24</v>
@@ -1082,7 +1081,7 @@
         <v>26</v>
       </c>
       <c r="O3" s="18" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="P3" s="23" t="s">
         <v>59</v>
@@ -1132,7 +1131,7 @@
         <v>21</v>
       </c>
       <c r="O4" s="18" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="P4" s="27" t="s">
         <v>58</v>
@@ -1155,13 +1154,13 @@
         <v>39</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G5" s="23" t="s">
         <v>45</v>
       </c>
       <c r="H5" s="18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I5" s="17" t="s">
         <v>19</v>
@@ -1202,13 +1201,13 @@
         <v>36</v>
       </c>
       <c r="F6" s="30" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I6" s="29" t="s">
         <v>37</v>
@@ -1220,13 +1219,13 @@
         <v>56</v>
       </c>
       <c r="L6" s="31" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M6" s="34" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N6" s="31" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="P6" s="31" t="s">
         <v>60</v>
@@ -1361,7 +1360,7 @@
         <v>37</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">

--- a/files/programming-tasks/programmieraufgaben_bechtel.xlsx
+++ b/files/programming-tasks/programmieraufgaben_bechtel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\hefl\files\programming-tasks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFDC9AEF-5842-41E0-A02B-4A75856D8CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8179E6-F6F1-4B2A-9037-FDA486AA7C5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15" yWindow="90" windowWidth="25875" windowHeight="20805" tabRatio="540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aufgaben" sheetId="1" r:id="rId1"/>
@@ -140,9 +140,6 @@
 #Deine Lösung</t>
   </si>
   <si>
-    <t>&lt;p&gt;Schreibe eine Funktion namens gruesse(name), die den Benutzer mit "Hallo, [Name]!" begrüßt. &lt;br&gt;&lt;br&gt; Setze den Gruß aus mehreren Strings zusammen und speichere sie in einer Variablen. Gib die Variable mit der korrekten Anrede mit dem Schlüsselwort 'return' zurück.. &lt;/p&gt;</t>
-  </si>
-  <si>
     <t>def gruesse(name):
     #Deine Lösung 
 print(gruesse("Anna"))</t>
@@ -159,16 +156,6 @@
 3. Ausnahme von der Ausnahme: Ein Jahr, das durch 400 teilbar ist, ist doch ein Schaltjahr.
 Erstelle eine Funktion ist_schaltjahr(jahr), die überprüft, ob ein gegebenes Jahr ein Schaltjahr ist 
 und entweder "Ist Schaltjahr." oder "Ist kein Schaltjahr."mit 'return' zurückgibt.</t>
-  </si>
-  <si>
-    <t>&lt;p&gt;Die Regel für Schaltjahre im gregorianischen Kalender ist wie folgt:
-&lt;br&gt;
-1. Ein Jahr, das durch 4 teilbar ist, ist ein Schaltjahr.&lt;br&gt;
-2. Ausnahme: Ein Jahr, das durch 100 teilbar ist, ist kein Schaltjahr.&lt;br&gt;
-3. Ausnahme von der Ausnahme: Ein Jahr, das durch 400 teilbar ist, ist doch ein Schaltjahr.
-&lt;/p&gt;&lt;br&gt;
-&lt;p&gt;Erstelle eine Funktion ist_schaltjahr(jahr), die überprüft, ob ein gegebenes Jahr ein Schaltjahr ist 
-und entweder "Ist Schaltjahr." oder "Ist kein Schaltjahr."mit 'return' zurückgibt.&lt;/p&gt;</t>
   </si>
   <si>
     <t>def ist_schaltjahr(jahr):
@@ -349,13 +336,6 @@
 Hinweis: Die Gesamtflaeche des Schachbretts ist die Summe der Flaechen aller 64 Quadrate.</t>
   </si>
   <si>
-    <t>&lt;p&gt;Ein Schachbrett besteht aus 8x8 Quadraten. Jedes Quadrat hat eine Seitenlänge von 2 cm. &lt;/p&gt;
-&lt;p&gt;Schreibe eine Funktion gesamtflaeche_schachbrett(), die die Gesamtflaeche des Schachbretts in Quadratzentimetern berechnet.&lt;/p&gt;&lt;br&gt;
-&lt;p&gt;Tipp: benutze eine Hilfsfunktion berechne_flaeche(), um zunächst die einzelnen Felder zu berechnen!&lt;/p&gt;&lt;br&gt;
-&lt;p&gt;Nutze dazu eine doppelt verschachtelte for-Schleife, um jedes Quadrat auf dem Schachbrett zu durchlaufen. Die Flaeche jedes Quadrats beträgt die Seitenlänge quadriert.&lt;/p&gt;&lt;br&gt;
-&lt;p&gt;Hinweis: Die Gesamtflaeche des Schachbretts ist die Summe der Flaechen aller 64 Quadrate.&lt;/p&gt;&lt;br&gt;</t>
-  </si>
-  <si>
     <t>gesamtflaeche_schachbrett</t>
   </si>
   <si>
@@ -384,16 +364,6 @@
 Erstelle eine Funktion berechne_gesamtpreis(einkaufsliste, preis_pro_gegenstand), die den Gesamtpreis des Einkaufs mithilfe einer for -Schleife berechnet.</t>
   </si>
   <si>
-    <t>&lt;p&gt;Wenn wir einer Liste ans Ende neue Elemente hinzufügen möchte, kann man die append()-Funktion verwenden. Man benutzt sie so:.&lt;/p&gt;
-&lt;p&gt;liste = ["Baum", "Wiese", "Garten"] &lt;br&gt;
-liste.append("Blumen")&lt;br&gt;
-print(liste)    # gibt ["Baum", "Wiese", "Garten", "Blumen"].&lt;/p&gt;
-&lt;p&gt;Erstelle eine Einkaufsliste wie gezeigt als Liste mit den Gegenständen Banane, Butter, Yoghurt, Käse und Milch. 
-Verlängere diese Liste dann mit der append.liste() Funktion und füge Nutella, Schokolade, Chips und Schinken hinzu.&lt;/p&gt;
-&lt;p&gt;In dem Supermarkt kostet alles 3 Euro. 
-Erstelle eine Funktion berechne_gesamtpreis(einkaufsliste, preis_pro_gegenstand), die den Gesamtpreis des Einkaufs mithilfe einer for -Schleife berechnet.&lt;/p&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">import unittest
 from schachbrett import  gesamtflaeche_schachbrett
 class TestGesamtflaecheSchachbrett(unittest.TestCase):
@@ -412,18 +382,55 @@
 </t>
   </si>
   <si>
-    <t>&lt;p&gt;Schreibe eine Funktion pizza_bestellung(pizza), die den Namen der Lieblingspizza eines Benutzers entgegennimmt und eine entsprechende Nachricht mit 'return' zurückgibt..&lt;/p&gt;
-&lt;br&gt;
-&lt;p&gt;Allerdings soll hier erstmal zwischen Margherita und Hawaii unterschieden werden.&lt;/p&gt;
-&lt;br&gt;
-&lt;p&gt;Bei Margherita soll: "Eine klassische Wahl! Gute Entscheidung.",
-bei Hawaii soll: "Ananas auf Pizza? Du bist mutig!" zurückgegeben werden.&lt;/p&gt;</t>
-  </si>
-  <si>
     <t>Schreibe eine Funktion pizza_bestellung(pizza), die den Namen der Lieblingspizza eines Benutzers entgegennimmt und eine entsprechende Nachricht mit 'return' zurückgibt.
 Allerdings soll hier erstmal zwischen Margherita und Hawaii unterschieden werden.
 Bei Margherita soll: "Eine klassische Wahl! Gute Entscheidung.",
 bei Hawaii soll: "Ananas auf Pizza? Du bist mutig!" ausgegeben werden.</t>
+  </si>
+  <si>
+    <t>Die Regel für Schaltjahre im gregorianischen Kalender ist wie folgt:
+1. Ein Jahr, das durch 4 teilbar ist, ist ein Schaltjahr.
+2. Ausnahme: Ein Jahr, das durch 100 teilbar ist, ist kein Schaltjahr.
+3. Ausnahme von der Ausnahme: Ein Jahr, das durch 400 teilbar ist, ist doch ein Schaltjahr.
+Erstelle eine Funktion `ist_schaltjahr(jahr)`, die überprüft, ob ein gegebenes Jahr ein Schaltjahr ist und entweder "Ist Schaltjahr." oder "Ist kein Schaltjahr." mit 'return' zurückgibt.</t>
+  </si>
+  <si>
+    <t>Ein Schachbrett besteht aus 8x8 Quadraten. Jedes Quadrat hat eine Seitenlänge von 2 cm.
+Schreibe eine Funktion `gesamtflaeche_schachbrett()`, die die Gesamtfläche des Schachbretts in Quadratzentimetern berechnet.
+Tipp: Benutze eine Hilfsfunktion `berechne_flaeche()`, um zunächst die einzelnen Felder zu berechnen!
+Nutze dazu eine doppelt verschachtelte `for`-Schleife, um jedes Quadrat auf dem Schachbrett zu durchlaufen. Die Fläche jedes Quadrats beträgt die Seitenlänge quadriert.
+Hinweis: Die Gesamtfläche des Schachbretts ist die Summe der Flächen aller 64 Quadrate.</t>
+  </si>
+  <si>
+    <t>Schreibe eine Funktion `pizza_bestellung(pizza)`, die den Namen der Lieblingspizza eines Benutzers entgegennimmt und eine entsprechende Nachricht mit `return` zurückgibt.
+### Details
+Die Funktion soll zunächst zwischen den beiden Pizzen "Margherita" und "Hawaii" unterscheiden.
+- **Margherita:** Bei Auswahl dieser Pizza sollte die folgende Nachricht zurückgegeben werden:
+  - `"Eine klassische Wahl! Gute Entscheidung."`
+- **Hawaii:** Bei der Wahl von Hawaii soll diese Nachricht zurückgegeben werden:
+  - `"Ananas auf Pizza? Du bist mutig!"`  
+Führe die Unterscheidung in der Funktion entsprechend aus.</t>
+  </si>
+  <si>
+    <t>Schreibe eine Funktion namens `gruesse(name)`, die den Benutzer mit "Hallo, [Name]!" begrüßt.
+- Setze den Gruß aus mehreren Strings zusammen und speichere sie in einer Variablen.
+- Gib die Variable mit der korrekten Anrede mit dem Schlüsselwort `return` zurück.</t>
+  </si>
+  <si>
+    <t>Wenn wir einer Liste am Ende neue Elemente hinzufügen möchten, können wir die `append()`-Funktion verwenden. Man benutzt sie so:
+```python
+liste = ["Baum", "Wiese", "Garten"]
+liste.append("Blumen")
+print(liste)  # gibt ["Baum", "Wiese", "Garten", "Blumen"]
+```
+### Aufgabe
+1. **Erstelle eine Einkaufsliste:**
+   - Erstelle eine Liste mit den Gegenständen: Banane, Butter, Yoghurt, Käse und Milch.
+2. **Verlängere die Liste:**
+   - Verwende die `append()`-Funktion und füge die Gegenstände hinzu: Nutella, Schokolade, Chips und Schinken.
+3. **Preisberechnung:**
+   - Im Supermarkt kostet alles 3 Euro.
+   - Erstelle eine Funktion `berechne_gesamtpreis(einkaufsliste, preis_pro_gegenstand)`, die den Gesamtpreis des Einkaufs mithilfe einer `for`-Schleife berechnet.</t>
   </si>
 </sst>
 </file>
@@ -518,7 +525,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -606,9 +613,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyBorder="1"/>
@@ -945,10 +949,10 @@
         <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>6</v>
@@ -969,13 +973,13 @@
         <v>11</v>
       </c>
       <c r="K1" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M1" t="s">
         <v>46</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="M1" t="s">
-        <v>48</v>
       </c>
       <c r="N1" t="s">
         <v>12</v>
@@ -984,7 +988,7 @@
         <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:16" s="23" customFormat="1" ht="285" x14ac:dyDescent="0.25">
@@ -995,7 +999,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D2" s="16">
         <v>9</v>
@@ -1007,10 +1011,10 @@
         <v>16</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="H2" s="21" t="s">
-        <v>28</v>
+        <v>41</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>75</v>
       </c>
       <c r="I2" s="18" t="s">
         <v>17</v>
@@ -1019,22 +1023,22 @@
         <v>0</v>
       </c>
       <c r="K2" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="L2" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="M2" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="N2" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="P2" s="23" t="s">
         <v>56</v>
-      </c>
-      <c r="L2" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="M2" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="N2" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="O2" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="P2" s="23" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:16" s="23" customFormat="1" ht="315" x14ac:dyDescent="0.25">
@@ -1045,7 +1049,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D3" s="16">
         <v>19</v>
@@ -1054,13 +1058,13 @@
         <v>23</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="H3" s="18" t="s">
-        <v>75</v>
+        <v>61</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="I3" s="21" t="s">
         <v>24</v>
@@ -1069,22 +1073,22 @@
         <v>0</v>
       </c>
       <c r="K3" s="23" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="L3" s="23" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="M3" s="23" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="N3" s="18" t="s">
         <v>26</v>
       </c>
       <c r="O3" s="18" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="P3" s="23" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:16" s="27" customFormat="1" ht="300" x14ac:dyDescent="0.25">
@@ -1095,22 +1099,22 @@
         <v>1</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D4" s="24">
         <v>19</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" s="25" t="s">
-        <v>32</v>
+        <v>42</v>
+      </c>
+      <c r="H4" t="s">
+        <v>72</v>
       </c>
       <c r="I4" s="17" t="s">
         <v>13</v>
@@ -1119,10 +1123,10 @@
         <v>0</v>
       </c>
       <c r="K4" s="27" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="L4" s="23" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M4" s="27">
         <v>2024</v>
@@ -1131,10 +1135,10 @@
         <v>21</v>
       </c>
       <c r="O4" s="18" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="P4" s="27" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:16" s="27" customFormat="1" ht="393" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1145,22 +1149,22 @@
         <v>1</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D5" s="24">
         <v>40</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="H5" s="18" t="s">
-        <v>72</v>
+        <v>43</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="I5" s="17" t="s">
         <v>19</v>
@@ -1169,22 +1173,22 @@
         <v>0</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="L5" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="M5" s="27" t="s">
         <v>53</v>
-      </c>
-      <c r="M5" s="27" t="s">
-        <v>55</v>
       </c>
       <c r="N5" s="23" t="s">
         <v>20</v>
       </c>
       <c r="P5" s="27" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" s="34" customFormat="1" ht="271.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="33" customFormat="1" ht="271.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="28">
         <v>10</v>
       </c>
@@ -1192,43 +1196,43 @@
         <v>1</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D6" s="28">
         <v>22</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F6" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="H6" t="s">
+        <v>73</v>
+      </c>
+      <c r="I6" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" s="32">
+        <v>0</v>
+      </c>
+      <c r="K6" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="L6" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="M6" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="N6" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="G6" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="H6" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="I6" s="29" t="s">
-        <v>37</v>
-      </c>
-      <c r="J6" s="33">
-        <v>0</v>
-      </c>
-      <c r="K6" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="L6" s="31" t="s">
-        <v>69</v>
-      </c>
-      <c r="M6" s="34" t="s">
-        <v>66</v>
-      </c>
-      <c r="N6" s="31" t="s">
-        <v>70</v>
-      </c>
       <c r="P6" s="31" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
@@ -1276,7 +1280,7 @@
         <v>17</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -1290,7 +1294,7 @@
         <v>24</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
@@ -1304,7 +1308,7 @@
         <v>13</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -1346,7 +1350,7 @@
         <v>19</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="7" customFormat="1" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1357,10 +1361,10 @@
         <v>10</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
